--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="projects" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="milestones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phase_map" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="projects" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="estimates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="milestones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="phase_map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="settings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,6 +966,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>案件ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>行程グループ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>見積人月</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【凡例】着手前の案件は実績が無く、要素別の見積もりだけが分かっている。ここに 行程グループ ごとの見積人月を入れると、その値がそのままグループ別の総量になる(設計書 6 Step1)。行を書かなかった行程グループは『この案件では行わない業務』として予測から除外される。1行も無ければ 契約人月 × 学習した工数比率 で配分する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1614,7 +1658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2301,7 +2345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,9 +9,8 @@
   <sheets>
     <sheet name="projects" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="estimates" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="milestones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="phase_map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="phase_map" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -464,6 +463,10 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,6 +510,26 @@
           <t>ステータス</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>プロトタイプ</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>α版</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>β版</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>マスターアップ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -547,6 +570,26 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2019-10-05</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2020-10-17</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2021-08-12</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -556,7 +599,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ブレイブフロンティア外伝</t>
+          <t>ブレイブフロンティア外伝(後半集中)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -587,6 +630,24 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-12</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2021-01-28</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -596,7 +657,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>クロノスギア</t>
+          <t>クロノスギア(二山)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -627,6 +688,26 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2021-01-15</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -636,7 +717,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>蒼穹のレガリア HD Edition</t>
+          <t>蒼穹のレガリア HD Edition(前倒し)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -667,6 +748,24 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2021-12-19</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -707,6 +806,26 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2021-10-25</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -747,6 +866,24 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2022-12-09</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -756,7 +893,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ギルドマスターズ</t>
+          <t>ギルドマスターズ(前倒し)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -787,6 +924,26 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-12</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -827,6 +984,24 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -867,6 +1042,24 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -876,7 +1069,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>オーヴァーロード・サーガ</t>
+          <t>オーヴァーロード・サーガ(後半集中)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -907,6 +1100,26 @@
           <t>完了</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -947,11 +1160,25 @@
           <t>予測対象</t>
         </is>
       </c>
+      <c r="I12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>【凡例】青字セルが手入力項目。タグは ; 区切りで複数指定可。ステータス=予測対象 の案件が予測の対象になる(実績CSVに行が無くてよい)。種別は必須・排他、タグは任意。</t>
+          <t>【凡例】青字セルが手入力項目。ステータス=予測対象 の案件が予測の対象になる(実績CSVに行が無くてよい)。ステータス列より右はマイルストーン列で、見出しがマイルストーン名、セルが日付(YYYY-MM-DD)。空欄=未記入で、記入が無くても動作する(設計書 3-2)。同じマイルストーンを一度で通過できず複数回訪れた場合は、見出しを α版 / α版#2 / α版#3 と増やす。最終回を工程の境目、初回を「α版(初回)」という別のマイルストーンとして扱う。</t>
         </is>
       </c>
     </row>
@@ -975,24 +1202,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>案件ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>行程グループ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>見積人月</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>【凡例】着手前の案件は実績が無く、要素別の見積もりだけが分かっている。ここに 行程グループ ごとの見積人月を入れると、その値がそのままグループ別の総量になる(設計書 6 Step1)。行を書かなかった行程グループは『この案件では行わない業務』として予測から除外される。1行も無ければ 契約人月 × 学習した工数比率 で配分する。</t>
         </is>
@@ -1004,661 +1231,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>案件ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>マイルストーン名</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2019-A</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2019-11-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2019-A</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2020-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2019-A</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2019-A</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2022-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-B</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-B</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-B</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2021-01-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-C</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2021-03-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-C</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-C</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2020-C</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2022-11-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-D</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-D</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2022-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-D</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2022-05-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-E</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-E</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-E</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2023-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2021-E</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-F</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-F</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2023-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-F</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-G</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>2022-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-G</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>2022-12-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-G</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2022-G</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>2023-12-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2023-H</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2023-H</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2023-H</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2023-I</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>2024-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2023-I</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2023-I</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2024-J</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2024-J</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2024-J</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2024-J</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>PJ-2026-K</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>2027-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>【凡例】青字セルが手入力項目。日付は YYYY-MM-DD。行が無い案件・無いマイルストーンがあっても動作する(設計書 3-2)。予測対象案件に行を書くと、その点は実測値として固定され前後は学習カーブで内挿される。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2345,13 +1917,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2460,37 +2032,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>マイルストーン最小件数</t>
+          <t>位置合わせ強度</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
+          <t>0〜1。実位置を正準位置へ引き戻す割合。下げると時間軸の伸縮が緩み、工数の跳ねが減る</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>カーブ解像度</t>
+          <t>伸縮率上限</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>正準時間軸の分割数。学習カーブのビン数</t>
+          <t>時間軸の伸縮率の上限(倍)。例 1.5。0=無制限。跳ねの高さに直接上限をかける</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>マイルストーン最小件数</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -2498,27 +2070,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>カーブ解像度</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>正準時間軸の分割数。学習カーブのビン数</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>タグ重み係数</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>タグ類似度の効き。第1版では未使用。実装順序 4 で使用する</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>【凡例】青字セルが手入力項目。k とタグ重み係数は設計書 9 の実装順序 3・4 で使用予定。第1版(素朴版+位置合わせ)では読み込むだけで計算に使わない。</t>
         </is>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1178,7 +1178,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>【凡例】青字セルが手入力項目。ステータス=予測対象 の案件が予測の対象になる(実績CSVに行が無くてよい)。ステータス列より右はマイルストーン列で、見出しがマイルストーン名、セルが日付(YYYY-MM-DD)。空欄=未記入で、記入が無くても動作する(設計書 3-2)。同じマイルストーンを一度で通過できず複数回訪れた場合は、見出しを α版 / α版#2 / α版#3 と増やす。最終回を工程の境目、初回を「α版(初回)」という別のマイルストーンとして扱う。</t>
+          <t>【凡例】青字セルが手入力項目。ステータス=予測対象 の案件が予測の対象になる(実績CSVに行が無くてよい)。ステータス列より右はマイルストーン列で、見出しがマイルストーン名、セルが日付(YYYY-MM-DD)。空欄=未記入で、記入が無くても動作する(設計書 3-2)。同じマイルストーンを一度で通過できず複数回訪れた場合は、同じセルにカンマ区切りで並べる(例: 2020-04-18, 2020-08-22)。列は増やさない。最終回を工程の境目、初回を「α版(初回)」という別のマイルストーンとして扱う。</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1923,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2032,95 +2032,112 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>位置合わせ強度</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
+          <t>マイルストーン精度</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0〜1。実位置を正準位置へ引き戻す割合。下げると時間軸の伸縮が緩み、工数の跳ねが減る</t>
+          <t>自動 / 月。月 にすると日付を月央に丸める(月まで表記に揃える)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>伸縮率上限</t>
+          <t>位置合わせ強度</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>時間軸の伸縮率の上限(倍)。例 1.5。0=無制限。跳ねの高さに直接上限をかける</t>
+          <t>0〜1。実位置を正準位置へ引き戻す割合。下げると時間軸の伸縮が緩み、工数の跳ねが減る</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>マイルストーン最小件数</t>
+          <t>伸縮率上限</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
+          <t>時間軸の伸縮率の上限(倍)。例 1.5。0=無制限。跳ねの高さに直接上限をかける</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>カーブ解像度</t>
+          <t>マイルストーン最小件数</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>正準時間軸の分割数。学習カーブのビン数</t>
+          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>カーブ解像度</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+          <t>正準時間軸の分割数。学習カーブのビン数</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>タグ重み係数</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>タグ類似度の効き。第1版では未使用。実装順序 4 で使用する</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>【凡例】青字セルが手入力項目。k とタグ重み係数は設計書 9 の実装順序 3・4 で使用予定。第1版(素朴版+位置合わせ)では読み込むだけで計算に使わない。</t>
         </is>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -572,22 +572,22 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2022-01</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-01</t>
         </is>
       </c>
     </row>
@@ -690,22 +690,22 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-10</t>
         </is>
       </c>
     </row>
@@ -753,17 +753,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2022-03-27</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-05</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-08</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2022-12-09</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08</t>
         </is>
       </c>
     </row>
@@ -926,22 +926,22 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-12</t>
         </is>
       </c>
     </row>
@@ -989,17 +989,17 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1047,17 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09</t>
         </is>
       </c>
     </row>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
+          <t>2027-07</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
@@ -1178,7 +1178,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>【凡例】青字セルが手入力項目。ステータス=予測対象 の案件が予測の対象になる(実績CSVに行が無くてよい)。ステータス列より右はマイルストーン列で、見出しがマイルストーン名、セルが日付(YYYY-MM-DD)。空欄=未記入で、記入が無くても動作する(設計書 3-2)。同じマイルストーンを一度で通過できず複数回訪れた場合は、同じセルにカンマ区切りで並べる(例: 2020-04-18, 2020-08-22)。列は増やさない。最終回を工程の境目、初回を「α版(初回)」という別のマイルストーンとして扱う。</t>
+          <t>【凡例】青字セルが手入力項目。ステータス=予測対象 の案件が予測の対象になる(実績CSVに行が無くてよい)。ステータス列より右はマイルストーン列で、見出しがマイルストーン名、セルが日付(YYYY-MM-DD)。空欄=未記入で、記入が無くても動作する(設計書 3-2)。同じマイルストーンを一度で通過できず複数回訪れた場合は、同じセルにカンマ区切りで並べる(例: 2020-04, 2020-08)。列は増やさない。最終回を工程の境目、初回を「α版(初回)」という別のマイルストーンとして扱う。</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>自動</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>自動 / 月。月 にすると日付を月央に丸める(月まで表記に揃える)</t>
+          <t>月 / 自動。既定の 月 は日付を月央に丸める。自動 は日まで書いた日付をそのまま使う</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -630,9 +630,7 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2020-09</t>
@@ -748,9 +746,7 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2021-12</t>
@@ -866,9 +862,7 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2022-12</t>
@@ -984,9 +978,7 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>2023-09</t>
@@ -1042,9 +1034,7 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>2024-01</t>
@@ -1160,20 +1150,14 @@
           <t>予測対象</t>
         </is>
       </c>
-      <c r="I12" s="3" t="n">
-        <v/>
-      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1923,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2079,65 +2063,81 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>マイルストーン最小件数</t>
+          <t>区間弾力性</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
+          <t>0〜0.9。マイルストーン区間への工数配分を区間の長さへ歩み寄らせる度合い。0=区間の工数比率を学習値のまま使う(設計書 3-1 の案A)。上げるほど極端に狭い区間への配分が減る。マイルストーンの日付は動かない</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>カーブ解像度</t>
+          <t>マイルストーン最小件数</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>正準時間軸の分割数。学習カーブのビン数</t>
+          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>カーブ解像度</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+          <t>正準時間軸の分割数。学習カーブのビン数</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>タグ重み係数</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B14" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>タグ類似度の効き。第1版では未使用。実装順序 4 で使用する</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>【凡例】青字セルが手入力項目。k とタグ重み係数は設計書 9 の実装順序 3・4 で使用予定。第1版(素朴版+位置合わせ)では読み込むだけで計算に使わない。</t>
         </is>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -630,7 +630,9 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n"/>
+      <c r="I3" s="3" t="n">
+        <v/>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2020-09</t>
@@ -746,7 +748,9 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n"/>
+      <c r="I5" s="3" t="n">
+        <v/>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2021-12</t>
@@ -862,7 +866,9 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="I7" s="3" t="n">
+        <v/>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2022-12</t>
@@ -978,7 +984,9 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="3" t="n">
+        <v/>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>2023-09</t>
@@ -1034,7 +1042,9 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n"/>
+      <c r="I10" s="3" t="n">
+        <v/>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>2024-01</t>
@@ -1150,14 +1160,20 @@
           <t>予測対象</t>
         </is>
       </c>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="3" t="n">
+        <v/>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
+      <c r="K12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1907,26 +1923,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>パラメータ</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1935,211 +1957,587 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>人月換算係数</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1人月あたりの時間。出力に必ず明記される(設計書 4-3)</t>
+          <t>入出力</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>実績CSV</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>実績CSVの場所。空欄ならマスタと同じフォルダの actuals.csv。相対パスはマスタのフォルダ基準(引数 --actuals が優先)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>集約軸</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>行程グループ</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>phase_map のどの列で学習するか。大分類 に変えると粗い粒度になる</t>
+          <t>入出力</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>出力先フォルダ</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>出力Excelを書き出すフォルダ。空欄なら output/(引数 --out-dir が優先)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>位置合わせ</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ON/OFF。マイルストーンによる landmark registration(設計書 5 Step3)</t>
+          <t>入出力</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>予測対象の案件ID</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>予測する案件を ; 区切りで指定する。空欄なら ステータス=予測対象 の案件をすべて出す。完了案件を書けば、その案件で予測の当たり具合を確かめられる(引数 --target が優先)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>背骨マイルストーン</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>位置合わせに使うマイルストーン名を ; 区切りで指定。自動=全案件共通のものを使う</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>人月換算係数</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1人月あたりの時間。出力に必ず明記される(設計書 4-3)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>背骨最小カバー率</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>この割合以上の案件が持つマイルストーンを背骨に採用する。1.0=全案件必須</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>集約軸</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>行程グループ</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>phase_map のどの列で学習するか。大分類 に変えると粗い粒度になる</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>マイルストーン精度</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>月 / 自動。既定の 月 は日付を月央に丸める。自動 は日まで書いた日付をそのまま使う</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>位置合わせ</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ON/OFF。マイルストーンによる landmark registration(設計書 5 Step3)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>位置合わせ強度</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0〜1。実位置を正準位置へ引き戻す割合。下げると時間軸の伸縮が緩み、工数の跳ねが減る</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>背骨マイルストーン</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>位置合わせに使うマイルストーン名を ; 区切りで指定。自動=全案件共通のものを使う</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>伸縮率上限</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>時間軸の伸縮率の上限(倍)。例 1.5。0=無制限。跳ねの高さに直接上限をかける</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>背骨最小カバー率</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>この割合以上の案件が持つマイルストーンを背骨に採用する。1.0=全案件必須</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>区間弾力性</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0〜0.9。マイルストーン区間への工数配分を区間の長さへ歩み寄らせる度合い。0=区間の工数比率を学習値のまま使う(設計書 3-1 の案A)。上げるほど極端に狭い区間への配分が減る。マイルストーンの日付は動かない</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>マイルストーン精度</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>月 / 自動。既定の 月 は日付を月央に丸める。自動 は日まで書いた日付をそのまま使う</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>マイルストーン最小件数</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>位置合わせ強度</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0〜1。実位置を正準位置へ引き戻す割合。下げると時間軸の伸縮が緩み、工数の跳ねが減る。ただしマイルストーンの山が指定日付からずれる</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>カーブ解像度</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>正準時間軸の分割数。学習カーブのビン数</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>伸縮率上限</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>時間軸の伸縮率の上限(倍)。例 1.5。0=無制限。跳ねの高さに直接上限をかける。ただしマイルストーンの山が指定日付からずれる</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>区間弾力性</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0〜1。学習データより狭く潰れたマイルストーン区間への工数配分を減らす度合い。0=区間の工数比率を学習値のまま使う(設計書 3-1 の案A)。1=区間が潰れたことによる密度上昇を完全に打ち消す。マイルストーンの日付は動かない</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>カーブ解像度</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>正準時間軸の分割数。学習カーブのビン数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>学習</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>カーブ復元</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>月内均等</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>月内均等 / 単調補間。月次の値から月の内側の分布をどう復元するか(設計書 5 Step2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>予測</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>見積もりを使う</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>ON/OFF。OFF にすると estimates シートを無視し、契約人月と学習比率だけで配分する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>予測</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>除外する行程グループ</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>この案件では行わない行程グループを ; 区切りで指定し、予測から外す。estimates シートに見積もりがある場合はそちらが優先される</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>予測</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>立ち上がり上限</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>月次工数の増加率の上限(前月比)。自動=実績の前月比90%点から決める / 数値(例 1.3) / off=制約なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>予測</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>立ち上がり上限の適用範囲</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>段階予測のみ</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>段階予測のみ / 全体 / なし。全体 にすると通常の予測と検証にも効く</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>段階予測</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>段階予測</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>自動 / ON / OFF。自動=実績とマイルストーンがある案件では出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>段階予測</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>段階予測の残工数</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>固定</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>固定 / 引き直す。固定=契約・見積もりの総量を動かさず 残り=総量-確定分 / 引き直す=確定分の実績から総量を推定し直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>段階予測</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>段階予測のマイルストーン</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>すべて</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>すべて / 通過済み。すべて=記入済みの日付を全部使う(「予測」シートと同じ条件) / 通過済み=その段階までに通過したものだけ(未来を覗かない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>検証・実行</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>検証</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ON/OFF。leave-one-out で予測の当たり具合を測り、検証シートに出す。OFF にすると速い</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>検証・実行</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>カーブ復元の比較</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ON/OFF。検証で 月内均等 と 単調補間 を並べて出すか</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>検証・実行</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>実績キャッシュ</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ON/OFF。実績CSVをparquetに読み込み済みとして再利用する。CSVを差し替えたら自動で作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>検証・実行</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>マイルストーン最小件数</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>この件数未満の統計は参考値として警告する(設計書 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>検証・実行</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>行程グループ最小件数</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>この件数未満の案件からしか学習できていない行程グループを警告する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>未使用</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>種別重み w=n/(n+k)。第1版では未使用。実装順序 3 で使用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>未使用</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>タグ重み係数</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="C29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>タグ類似度の効き。第1版では未使用。実装順序 4 で使用する</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>【凡例】青字セルが手入力項目。k とタグ重み係数は設計書 9 の実装順序 3・4 で使用予定。第1版(素朴版+位置合わせ)では読み込むだけで計算に使わない。</t>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>【凡例】青字セルが手入力項目。空欄にすると既定値で動く。コマンドライン引数を渡した場合は、そちらがこのシートより優先される。区分=未使用 の k とタグ重み係数は設計書 9 の実装順序 3・4 で使用予定で、第1版(素朴版+位置合わせ)では読み込むだけで計算に使わない。</t>
         </is>
       </c>
     </row>
